--- a/03_OUTPUT/analise_consolidada.xlsx
+++ b/03_OUTPUT/analise_consolidada.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:R103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,42 +435,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>nivel_risco</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>cpf</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>process_number</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>tipo_acao</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>situacao_processual</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>vara</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>foro</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>raw_text</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>text_source</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>table_count</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>processes_geometric</t>
         </is>
       </c>
     </row>
@@ -488,19 +523,38 @@
           <t>desconhecido</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fitz</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>plumber</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -514,27 +568,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>desconhecido</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>informativo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>é sócio</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Secretaria da Fazenda e Planejamento do Estado
 de São Paulo
@@ -555,13 +623,18 @@
 Folha 1 de 1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -575,27 +648,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>desconhecido</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>informativo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>ISMAEL DA SILVA CPF</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>MINISTÉRIO DA FAZENDA
 Secretaria da Receita Federal do Brasil
@@ -623,13 +710,18 @@
 Qualquer rasura ou emenda invalidará este documento.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -648,18 +740,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>informativo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>do aluno RG do aluno RA do aluno Métodos utilizados</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>18/03/2026, 20:44 Extracao_Atestados_Donut_OCR_Organizado_corrigido.ipynb - Colab
  Extração de Nome, RG e RA em Atestados de Matrícula
@@ -721,13 +827,18 @@
 https://colab.research.google.com/drive/1KhHRG8298Pj_uixU9UiZ64HEAS4_Qw50#scrollTo=e1MKqAuI64tf&amp;printMode=true 1/4</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="Q5" t="n">
         <v>2</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -744,16 +855,30 @@
           <t>desconhecido</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>18/03/2026, 20:44 Extracao_Atestados_Donut_OCR_Organizado_corrigido.ipynb - Colab
 nome_base = os.path.splitext(os.path.basename(caminho_pdf))[0]
@@ -821,13 +946,18 @@
 https://colab.research.google.com/drive/1KhHRG8298Pj_uixU9UiZ64HEAS4_Qw50#scrollTo=e1MKqAuI64tf&amp;printMode=true 2/4</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="Q6" t="n">
         <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -846,18 +976,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>informativo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>if nome else None</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>18/03/2026, 20:44 Extracao_Atestados_Donut_OCR_Organizado_corrigido.ipynb - Colab
 outputs = model.generate(
@@ -927,13 +1071,18 @@
 https://colab.research.google.com/drive/1KhHRG8298Pj_uixU9UiZ64HEAS4_Qw50#scrollTo=e1MKqAuI64tf&amp;printMode=true 3/4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="Q7" t="n">
         <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -950,16 +1099,30 @@
           <t>desconhecido</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>18/03/2026, 20:44 Extracao_Atestados_Donut_OCR_Organizado_corrigido.ipynb - Colab
 Processando: e30b3a51-1cb8-4f2b-a316-3bd64d2e2638.pdf
@@ -999,13 +1162,18 @@
 https://colab.research.google.com/drive/1KhHRG8298Pj_uixU9UiZ64HEAS4_Qw50#scrollTo=e1MKqAuI64tf&amp;printMode=true 4/4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="Q8" t="n">
         <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1022,16 +1190,30 @@
           <t>desconhecido</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>19/12/1955</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>PONTIFÍCIA UNIVERSIDADE CATÓLICA DE CAMPINAS
 Reconhecida pelos Decretos nº 38.327 de 19/12/1955, D.O.U de 28/12/1955, col. 3, p. 23.673 e nº 48.689 de
@@ -1051,13 +1233,18 @@
 18/03/2026 20:21:53 Página 1 de 1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="Q9" t="n">
         <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1076,14 +1263,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>informativo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>do aluno</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Análise Comparativa com Base nos Resultados Obtidos
 A análise dos resultados experimentais permite uma avaliação mais concreta do
@@ -1123,13 +1324,18 @@
 resposta.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="Q10" t="n">
         <v>0</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1148,14 +1354,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>informativo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>do aluno</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>A análise empírica, portanto, confirma que, para o conjunto de documentos testados, o método
 de OCR com Tesseract e regex foi mais eficiente e confiável na extração completa das
@@ -1164,13 +1384,18 @@
 nome do aluno.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="Q11" t="n">
         <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1184,19 +1409,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>desconhecido</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>informativo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>de Ismael da Silva</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>0000332883
 PODER JUDICIÁRIO
@@ -1222,13 +1461,18 @@
 vigente.</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="Q12" t="n">
         <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1242,31 +1486,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>criminal_estadual</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Justiça Pública</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>164.564.498-71</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>1501506-68.2025.8.26.0548</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>10/02/2026</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>0093957451
 10/02/2026
@@ -1312,13 +1570,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="Q13" t="n">
         <v>0</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1332,19 +1595,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>criminal_estadual</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>10/02/2026</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>0093957451
 10/02/2026
@@ -1359,13 +1636,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="Q14" t="n">
         <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1379,31 +1661,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>criminal_estadual</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pesquisado</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Pesquisado</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>0004372-48.1994.8.26.0116</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>0095363191
 31/03/2026
@@ -1452,13 +1748,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="Q15" t="n">
         <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1472,19 +1773,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>criminal_estadual</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>0095363191
 31/03/2026
@@ -1502,13 +1817,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="Q16" t="n">
         <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1522,31 +1842,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>civel_estadual</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>em nome de</t>
+          <t>maximo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Em Nome De</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>300.892.878-19</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>0013096-12.2005.8.26.0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -1605,13 +1939,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="Q17" t="n">
         <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['0034496-59.1980.8.26.0001', '0034613-94.1973.8.26.0001', '0034650-97.1968.8.26.0001', '0034653-52.1968.8.26.0001', '0034655-85.1969.8.26.0001', '0034675-76.1969.8.26.0001', '0034676-61.1969.8.26.0001', '0034677-46.1969.8.26.0001']</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1625,23 +1964,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>0034712-64.1973.8.26.0001</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -1712,13 +2065,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="Q18" t="n">
         <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['0034712-64.1973.8.26.0001', '0034713-83.1972.8.26.0001', '0034714-68.1972.8.26.0001', '0036526-62.1983.8.26.0001', '0036535-24.1983.8.26.0001', '0105364-42.1992.8.26.0001', '0109544-77.1987.8.26.0001', '0109692-15.1992.8.26.0001', '0110561-22.1985.8.26.0001', '0112334-29.1990.8.26.0001', '0114680-26.1985.8.26.0001', '0115718-68.1988.8.26.0001']</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1732,23 +2090,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>0117298-70.1987.8.26.0001</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -1818,13 +2190,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="Q19" t="n">
         <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['0117298-70.1987.8.26.0001', '0119725-69.1989.8.26.0001', '0124616-26.1995.8.26.0001', '0126624-49.1990.8.26.0001', '0127579-80.1990.8.26.0001', '0136278-65.1987.8.26.0001']</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1838,23 +2215,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>0011616-98.2002.8.26.0002</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -1925,13 +2316,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="Q20" t="n">
         <v>0</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1945,23 +2341,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>0046948-97.2000.8.26.0002</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2032,13 +2442,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="Q21" t="n">
         <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2052,23 +2467,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>0160074-09.1992.8.26.0002</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2139,13 +2568,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="Q22" t="n">
         <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2159,23 +2593,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>0527287-95.1988.8.26.0002</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2246,13 +2694,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="Q23" t="n">
         <v>0</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['0016153-05.2000.8.26.0004', '0034468-19.1979.8.26.0004', '0034473-41.1979.8.26.0004', '0034487-93.1977.8.26.0004', '0034497-06.1978.8.26.0004']</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2266,23 +2719,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>0034500-58.1978.8.26.0004</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2353,13 +2820,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="Q24" t="n">
         <v>0</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['0034500-58.1978.8.26.0004', '0034501-43.1978.8.26.0004', '0034506-65.1978.8.26.0004', '0034508-35.1978.8.26.0004', '0034515-27.1978.8.26.0004', '0034521-34.1978.8.26.0004', '0034540-45.1975.8.26.0004', '0034553-10.1976.8.26.0004', '0034574-49.1977.8.26.0004', '0034579-71.1977.8.26.0004', '0034598-53.1972.8.26.0004', '0034659-84.1967.8.26.0004', '0034669-60.1969.8.26.0004', '0034728-91.1982.8.26.0004', '0034733-16.1982.8.26.0004', '0036637-70.2002.8.26.0004']</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2373,23 +2845,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>0103879-86.1978.8.26.0004</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2459,13 +2945,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="Q25" t="n">
         <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['0103879-86.1978.8.26.0004', '0226400-18.1987.8.26.0004', '0234365-71.1992.8.26.0004', '0237838-70.1989.8.26.0004', '0245822-03.1992.8.26.0004', '0351176-61.1985.8.26.0004', '0967170-80.1985.8.26.0004']</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2479,23 +2970,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>0002315-55.2001.8.26.0005</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2566,13 +3071,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K26" t="n">
+      <c r="Q26" t="n">
         <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2586,23 +3096,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>0261664-15.1995.8.26.0005</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2673,13 +3197,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K27" t="n">
+      <c r="Q27" t="n">
         <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2693,23 +3222,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>0003329-53.2010.8.26.0007</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2780,13 +3323,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K28" t="n">
+      <c r="Q28" t="n">
         <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['0034450-52.1980.8.26.0007', '0034478-54.1979.8.26.0007', '0034512-63.1978.8.26.0007', '0034516-03.1978.8.26.0007', '0034522-10.1978.8.26.0007', '0034525-62.1978.8.26.0007', '0034726-15.1982.8.26.0007', '0034729-67.1982.8.26.0007', '0036537-73.1983.8.26.0007', '0112834-87.1984.8.26.0007', '0112836-57.1984.8.26.0007']</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2800,23 +3348,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>0112837-42.1984.8.26.0007</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2887,13 +3449,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K29" t="n">
+      <c r="Q29" t="n">
         <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['0112837-42.1984.8.26.0007', '0112840-31.1983.8.26.0007', '0301334-59.1992.8.26.0007', '0303819-71.1988.8.26.0007', '0307269-70.1998.8.26.0007', '0308058-89.1986.8.26.0007', '0310441-88.1996.8.26.0007', '0311009-46.1992.8.26.0007', '0318345-62.1996.8.26.0007', '0935592-90.1985.8.26.0007', '0034555-65.1976.8.26.0008', '0034684-80.1970.8.26.0008', '0034694-27.1970.8.26.0008']</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2907,23 +3474,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>0034752-44.1981.8.26.0008</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -2994,13 +3575,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K30" t="n">
+      <c r="Q30" t="n">
         <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['0036531-63.1983.8.26.0008', '0036551-79.1968.8.26.0008', '0325588-25.1994.8.26.0008', '0329566-54.1987.8.26.0008']</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -3014,23 +3600,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>0034704-34.1971.8.26.0009</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -3101,13 +3701,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K31" t="n">
+      <c r="Q31" t="n">
         <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['0034519-46.1978.8.26.0010', '0034550-37.1976.8.26.0010', '0034561-66.1976.8.26.0010', '0036534-12.1983.8.26.0010', '0112838-18.1984.8.26.0010', '0378006-12.1986.8.26.0010']</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -3121,23 +3726,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>0451350-52.1988.8.26.0011</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -3205,13 +3824,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K32" t="n">
+      <c r="Q32" t="n">
         <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['0034538-78.1980.8.26.0011', '0034578-65.1977.8.26.0011', '0034471-50.1979.8.26.0011', '0034485-05.1977.8.26.0011', '0457018-04.1988.8.26.0011', '0458907-90.1988.8.26.0011', '0034494-59.1980.8.26.0011', '0005238-80.1999.8.26.0019', '0002426-95.1995.8.26.0022']</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -3225,23 +3849,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>0002426-95.1995.8.26.0022</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -3307,13 +3945,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K33" t="n">
+      <c r="Q33" t="n">
         <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['0004392-49.2002.8.26.0022', '0003002-04.2003.8.26.0024', '0000653-25.1994.8.26.0030', '0008619-52.2002.8.26.0032', '0001811-16.2002.8.26.0037', '0011436-24.2014.8.26.0047', '0012438-44.2005.8.26.0047']</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -3327,23 +3970,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>0013217-91.2008.8.26.0047</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -3414,13 +4071,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K34" t="n">
+      <c r="Q34" t="n">
         <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['0013217-91.2008.8.26.0047', '0015542-63.2013.8.26.0047', '0015877-19.2012.8.26.0047', '0018083-40.2011.8.26.0047', '0018086-92.2011.8.26.0047', '0021429-62.2012.8.26.0047']</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -3434,23 +4096,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>0121596-11.2008.8.26.0053</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -3518,13 +4194,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K35" t="n">
+      <c r="Q35" t="n">
         <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['0001071-51.2000.8.26.0062', '0002752-83.1996.8.26.0066', '0005205-80.1998.8.26.0066', '0001060-14.1994.8.26.0068', '0004892-55.1994.8.26.0068', '0014127-16.2012.8.26.0068', '0000243-87.1984.8.26.0071']</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -3538,23 +4219,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>0000290-95.1983.8.26.0071</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -3622,13 +4317,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K36" t="n">
+      <c r="Q36" t="n">
         <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>['0000290-95.1983.8.26.0071', '0000315-40.1985.8.26.0071', '0000491-09.1991.8.26.0071', '0001160-24.1975.8.26.0071', '0012203-10.2002.8.26.0071', '0019914-13.1995.8.26.0071', '0022182-35.1998.8.26.0071', '0003122-73.1998.8.26.0072', '0004330-29.1997.8.26.0072', '1004629-80.2020.8.26.0072', '0006623-15.2001.8.26.0077']</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3642,23 +4342,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>0009850-81.1999.8.26.0077</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -3726,13 +4440,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K37" t="n">
+      <c r="Q37" t="n">
         <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['1003302-12.2025.8.26.0077', '0001232-29.2008.8.26.0079', '0003236-68.2010.8.26.0079', '0005860-27.2009.8.26.0079', '0008308-17.2002.8.26.0079', '0010972-21.2002.8.26.0079', '1000893-43.2014.8.26.0079', '1000893-43.2014.8.26.0079', '2000543-39.1994.8.26.0079', '2000564-64.1984.8.26.0079', '2000606-35.1992.8.26.0079', '0034451-31.1979.8.26.0085', '0034458-52.1981.8.26.0085', '0034477-29.1979.8.26.0085']</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3746,23 +4465,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>0034482-22.1977.8.26.0085</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -3832,13 +4565,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K38" t="n">
+      <c r="Q38" t="n">
         <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>['0034482-22.1977.8.26.0085', '0034483-07.1977.8.26.0085', '0034502-76.1978.8.26.0085', '0034505-65.1977.8.26.0085', '0034509-68.1978.8.26.0085', '0034511-38.1978.8.26.0085', '0034524-37.1978.8.26.0085', '0034529-88.1980.8.26.0085', '0034542-63.1975.8.26.0085', '0034548-36.1976.8.26.0085', '0034549-21.1976.8.26.0085', '0034569-12.1976.8.26.0085', '0034584-44.1977.8.26.0085', '0034585-97.1975.8.26.0085', '0034593-74.1975.8.26.0085', '0034595-44.1975.8.26.0085', '0034607-29.1973.8.26.0085', '0034622-61.1974.8.26.0085', '0034628-68.1974.8.26.0085']</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -3852,23 +4590,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>0034718-42.1975.8.26.0085</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -3939,13 +4691,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K39" t="n">
+      <c r="Q39" t="n">
         <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>['0034718-42.1975.8.26.0085', '0034719-90.1976.8.26.0085', '0034720-12.1975.8.26.0085', '0034727-57.1982.8.26.0085', '0036533-30.1982.8.26.0085', '0134635-19.1984.8.26.0085', '0346374-05.1984.8.26.0085', '0034454-12.1981.8.26.0086', '0034455-94.1981.8.26.0086', '0034456-45.1982.8.26.0086', '0034461-04.1981.8.26.0086', '0034462-86.1981.8.26.0086', '0034467-79.1979.8.26.0086', '0034475-56.1979.8.26.0086', '0034528-03.1980.8.26.0086', '0034556-10.1976.8.26.0086', '0034557-92.1976.8.26.0086', '0034565-25.1983.8.26.0086', '0034571-76.1976.8.26.0086', '0034612-48.1973.8.26.0086']</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -3959,23 +4716,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>0034693-02.1970.8.26.0086</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -4046,13 +4817,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K40" t="n">
+      <c r="Q40" t="n">
         <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>['0034693-02.1970.8.26.0086', '0034700-57.1971.8.26.0086', '0034730-09.1982.8.26.0086', '0034747-11.1983.8.26.0086', '0034751-19.1981.8.26.0086', '0034761-97.1980.8.26.0086', '0036536-45.1983.8.26.0086', '0036538-15.1983.8.26.0086', '0036539-97.1983.8.26.0086', '0346345-49.1984.8.26.0086', '0347314-64.1984.8.26.0086', '0034533-19.1980.8.26.0088', '0034592-80.1975.8.26.0088', '0034623-37.1974.8.26.0088', '0034745-69.1982.8.26.0088', '0034748-87.1983.8.26.0088', '0034760-09.1980.8.26.0088', '0112835-23.1984.8.26.0088', '0034447-79.1979.8.26.0089']</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -4066,23 +4842,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>0034453-18.1981.8.26.0089</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -4153,13 +4943,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K41" t="n">
+      <c r="Q41" t="n">
         <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>['0034453-18.1981.8.26.0089', '0034463-62.1981.8.26.0089', '0034495-04.1980.8.26.0089', '0034499-12.1978.8.26.0089', '0034513-93.1978.8.26.0089', '0034552-61.1976.8.26.0089', '0034568-15.1976.8.26.0089', '0034580-92.1977.8.26.0089', '0034609-84.1973.8.26.0089', '0034611-54.1973.8.26.0089', '0034615-57.1974.8.26.0089', '0034632-93.1974.8.26.0089', '0034654-64.1968.8.26.0089', '0034662-07.1969.8.26.0089', '0034664-74.1969.8.26.0089', '0034673-36.1969.8.26.0089', '0034674-21.1969.8.26.0089', '0034681-76.1970.8.26.0089', '0034683-46.1970.8.26.0089', '0034685-16.1970.8.26.0089']</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -4173,23 +4968,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t>0034687-83.1970.8.26.0089</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -4260,13 +5069,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K42" t="n">
+      <c r="Q42" t="n">
         <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>['0034687-83.1970.8.26.0089', '0034691-23.1970.8.26.0089', '0034698-78.1971.8.26.0089', '0034699-63.1971.8.26.0089', '0034702-81.1972.8.26.0089', '0034703-03.1971.8.26.0089', '0034722-72.1972.8.26.0089', '0034757-51.1980.8.26.0089', '0036524-22.1983.8.26.0089', '0346334-11.1984.8.26.0089']</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -4280,23 +5094,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
         <is>
           <t>0144252-24.0100.8.26.0090</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -4366,13 +5194,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K43" t="n">
+      <c r="Q43" t="n">
         <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>['0007332-45.1982.8.26.0100', '0016271-43.1984.8.26.0100', '0022674-96.1982.8.26.0100', '0033105-29.1981.8.26.0100', '0034448-31.1979.8.26.0100', '0034449-79.1980.8.26.0100', '0034452-34.1980.8.26.0100']</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -4386,23 +5219,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
         <is>
           <t>0034474-29.1979.8.26.0100</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -4473,13 +5320,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K44" t="n">
+      <c r="Q44" t="n">
         <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>['0034474-29.1979.8.26.0100', '0034476-96.1979.8.26.0100', '0034480-70.1978.8.26.0100', '0034481-21.1979.8.26.0100', '0034486-14.1977.8.26.0100', '0034491-31.1980.8.26.0100', '0034492-16.1980.8.26.0100', '0034503-16.1978.8.26.0100', '0034507-53.1978.8.26.0100', '0034517-97.1978.8.26.0100', '0034518-82.1978.8.26.0100', '0034527-73.1980.8.26.0100', '0034530-28.1980.8.26.0100', '0034531-13.1980.8.26.0100', '0034534-65.1980.8.26.0100', '0034535-50.1980.8.26.0100', '0034536-35.1980.8.26.0100', '0034537-20.1980.8.26.0100', '0034544-51.1976.8.26.0100']</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -4493,23 +5345,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t>0034546-21.1976.8.26.0100</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -4580,13 +5446,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K45" t="n">
+      <c r="Q45" t="n">
         <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>['0034546-21.1976.8.26.0100', '0034547-06.1976.8.26.0100', '0034551-43.1976.8.26.0100', '0034562-72.1976.8.26.0100', '0034563-57.1976.8.26.0100', '0034572-82.1977.8.26.0100', '0034573-67.1977.8.26.0100', '0034581-44.1977.8.26.0100', '0034583-14.1977.8.26.0100', '0034588-07.1975.8.26.0100', '0034589-89.1975.8.26.0100', '0034591-59.1975.8.26.0100', '0034594-14.1975.8.26.0100', '0034601-74.1973.8.26.0100', '0034602-59.1973.8.26.0100', '0034605-14.1973.8.26.0100', '0034610-36.1973.8.26.0100', '0034614-39.1974.8.26.0100', '0034616-43.1973.8.26.0100', '0034627-38.1974.8.26.0100']</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -4600,23 +5471,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t>0034638-48.1966.8.26.0100</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -4687,13 +5572,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="Q46" t="n">
         <v>0</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>['0034638-48.1966.8.26.0100', '0034639-33.1966.8.26.0100', '0034641-03.1966.8.26.0100', '0034643-36.1967.8.26.0100', '0034644-50.1969.8.26.0100', '0034645-35.1969.8.26.0100', '0034647-39.1968.8.26.0100', '0034649-09.1968.8.26.0100', '0034652-61.1968.8.26.0100', '0034657-83.1968.8.26.0100', '0034665-26.1969.8.26.0100', '0034666-11.1969.8.26.0100', '0034672-18.1969.8.26.0100', '0034686-65.1970.8.26.0100', '0034688-35.1970.8.26.0100', '0034689-20.1970.8.26.0100', '0034690-05.1970.8.26.0100', '0034695-56.1972.8.26.0100']</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -4707,23 +5597,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>0034697-26.1972.8.26.0100</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -4794,13 +5698,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K47" t="n">
+      <c r="Q47" t="n">
         <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>['0034697-26.1972.8.26.0100', '0034701-97.1971.8.26.0100', '0034705-37.1971.8.26.0100', '0034707-07.1971.8.26.0100', '0034711-73.1973.8.26.0100']</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -4814,23 +5723,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
         <is>
           <t>0034769-71.1976.8.26.0100</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -4901,13 +5824,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K48" t="n">
+      <c r="Q48" t="n">
         <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>['0036527-71.1965.8.26.0100', '0036540-70.1965.8.26.0100', '0043015-75.1984.8.26.0100', '0047102-74.1984.8.26.0100', '0054564-19.1983.8.26.0100', '0075688-29.1981.8.26.0100', '0084479-16.1983.8.26.0100', '0084688-82.1983.8.26.0100', '0088807-86.1983.8.26.0100', '0089762-20.1983.8.26.0100']</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -4921,23 +5849,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
         <is>
           <t>0102502-15.1980.8.26.0100</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5008,13 +5950,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K49" t="n">
+      <c r="Q49" t="n">
         <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>['0102502-15.1980.8.26.0100', '0110627-69.1980.8.26.0100', '0235962-19.2008.8.26.0100', '0305268-18.1984.8.26.0100', '0741378-91.1997.8.26.0100', '0742972-09.1998.8.26.0100', '0800889-74.1984.8.26.0100', '0801900-94.1991.8.26.0100']</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -5028,27 +5975,41 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>civel_estadual</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ação</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
+          <t>maximo</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ação</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
         <is>
           <t>0802189-27.1991.8.26.0100</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5118,13 +6079,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K50" t="n">
+      <c r="Q50" t="n">
         <v>0</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>['0813599-14.1993.8.26.0100', '0900100-76.1930.8.26.0100', '0900389-18.1944.8.26.0100', '0900390-03.1944.8.26.0100', '0901797-43.1964.8.26.0100', '0902090-52.1960.8.26.0100', '0902905-78.1962.8.26.0100', '0903170-46.1963.8.26.0100', '0903600-61.1964.8.26.0100', '0903601-46.1964.8.26.0100', '0903602-31.1964.8.26.0100', '0907830-60.1938.8.26.0100', '0908642-90.1984.8.26.0100']</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -5138,23 +6104,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
         <is>
           <t>0909838-09.1958.8.26.0100</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5220,13 +6200,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K51" t="n">
+      <c r="Q51" t="n">
         <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>['0909838-09.1958.8.26.0100', '1001647-27.2025.8.26.0102', '0004331-61.2010.8.26.0103', '0002715-77.1994.8.26.0114', '0004920-64.2003.8.26.0114', '0007043-84.1993.8.26.0114', '0012897-54.1996.8.26.0114', '0017410-07.1992.8.26.0114', '0024358-91.1994.8.26.0114', '0027774-67.1994.8.26.0114']</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -5240,27 +6225,41 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>civel_estadual</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Jose Luiz da Silva Filho</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
+          <t>maximo</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Jose Luiz Da Silva Filho</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
         <is>
           <t>1003261-38.2019.8.26.0115</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5328,13 +6327,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K52" t="n">
+      <c r="Q52" t="n">
         <v>0</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>['1003261-38.2019.8.26.0115', '0000585-63.2003.8.26.0126', '0001595-64.2011.8.26.0126', '0000130-57.1987.8.26.0127', '0003845-58.1997.8.26.0127', '0004881-28.2003.8.26.0127', '0006038-89.2010.8.26.0127', '0001259-52.2005.8.26.0132', '0001531-32.1994.8.26.0132', '0007510-38.1995.8.26.0132']</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -5348,23 +6352,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
         <is>
           <t>0000034-11.1980.8.26.0152</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5431,13 +6449,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K53" t="n">
+      <c r="Q53" t="n">
         <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>['0000034-11.1980.8.26.0152', '0004289-46.1979.8.26.0152', '0017792-16.2011.8.26.0152', '0001976-69.2003.8.26.0153', '0000345-38.2004.8.26.0159', '0001437-58.1998.8.26.0160', '0000106-87.1988.8.26.0161', '0006076-92.1993.8.26.0161', '0006746-23.1999.8.26.0161', '0009856-69.1995.8.26.0161', '0014200-39.2008.8.26.0161', '0015290-92.2002.8.26.0161', '0020381-32.2003.8.26.0161', '0505996-46.2008.8.26.0161']</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -5451,23 +6474,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
         <is>
           <t>0000231-19.1997.8.26.0168</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5537,13 +6574,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K54" t="n">
+      <c r="Q54" t="n">
         <v>0</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>['0000231-19.1997.8.26.0168', '0001943-58.2008.8.26.0168', '0001461-14.1993.8.26.0176', '0004865-24.2003.8.26.0176', '0005385-52.2001.8.26.0176', '0008212-70.2000.8.26.0176', '1008520-49.2024.8.26.0176']</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -5557,23 +6599,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
         <is>
           <t>1512262-69.2017.8.26.0176</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5641,13 +6697,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K55" t="n">
+      <c r="Q55" t="n">
         <v>0</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>['0002692-73.2007.8.26.0180', '0001126-13.1994.8.26.0191', '0002596-64.1994.8.26.0196', '0003489-50.1997.8.26.0196']</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -5661,23 +6722,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
         <is>
           <t>0006348-73.1996.8.26.0196</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5744,13 +6819,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K56" t="n">
+      <c r="Q56" t="n">
         <v>0</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>['0007418-81.2003.8.26.0196', '0041502-11.2003.8.26.0196', '0500525-75.2007.8.26.0196', '0511202-04.2006.8.26.0196', '0600871-87.2014.8.26.0196', '1009567-76.2016.8.26.0196', '0000561-40.2008.8.26.0197', '0001486-56.1996.8.26.0197', '0002295-09.1997.8.26.0198', '0005349-44.2011.8.26.0213', '0005318-77.2000.8.26.0223']</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -5764,23 +6844,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
         <is>
           <t>0007161-50.1998.8.26.0093</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5850,13 +6944,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K57" t="n">
+      <c r="Q57" t="n">
         <v>0</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>['0007161-50.1998.8.26.0093', '0011458-98.1998.8.26.0223', '0012827-85.2005.8.26.0093', '0522628-48.2014.8.26.0223', '0524660-26.2014.8.26.0223', '0533499-11.2012.8.26.0223', '0539005-70.2009.8.26.0223', '0541836-91.2009.8.26.0223', '1526236-61.2019.8.26.0223', '0000015-94.1991.8.26.0224', '0000020-98.1963.8.26.0224', '0000051-25.1980.8.26.0224', '0000077-62.1976.8.26.0224', '0000095-30.1969.8.26.0224', '0000098-67.1978.8.26.0224', '0000105-54.1981.8.26.0224', '0000147-40.1980.8.26.0224', '0000150-53.1984.8.26.0224', '0000154-12.1992.8.26.0224']</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -5870,23 +6969,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
         <is>
           <t>0000154-12.1992.8.26.0224</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -5957,13 +7070,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K58" t="n">
+      <c r="Q58" t="n">
         <v>0</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>['0000208-90.1983.8.26.0224', '0000219-85.1984.8.26.0224', '0000257-34.1983.8.26.0224', '0000310-49.1982.8.26.0224', '0000336-52.1979.8.26.0224', '0000355-82.1984.8.26.0224', '0000431-38.1986.8.26.0224', '0000501-31.1981.8.26.0224', '0000511-65.1987.8.26.0224', '0000584-82.1960.8.26.0224', '0000660-66.1984.8.26.0224', '0000683-12.1984.8.26.0224', '0000908-32.1984.8.26.0224', '0000908-66.1983.8.26.0224', '0000909-17.1984.8.26.0224', '0001062-50.1984.8.26.0224', '0001098-19.1989.8.26.0224', '0001313-05.1983.8.26.0224', '0001330-65.1988.8.26.0224']</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -5977,23 +7095,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
         <is>
           <t>0001523-27.1981.8.26.0224</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6063,13 +7195,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K59" t="n">
+      <c r="Q59" t="n">
         <v>0</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>['0001523-27.1981.8.26.0224', '0001662-95.1989.8.26.0224', '0001706-17.1989.8.26.0224', '0001822-52.1991.8.26.0224', '0007382-92.1979.8.26.0224', '0008084-95.2003.8.26.0224', '0008862-32.1984.8.26.0224', '0012920-97.1992.8.26.0224', '0017559-61.1992.8.26.0224', '1009572-04.2022.8.26.0224', '0002525-76.2007.8.26.0238', '0013085-53.2002.8.26.0238']</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -6083,23 +7220,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
         <is>
           <t>0013088-08.2002.8.26.0238</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6165,13 +7316,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K60" t="n">
+      <c r="Q60" t="n">
         <v>0</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>['0013088-08.2002.8.26.0238', '0002680-02.2010.8.26.0262', '0000565-10.2007.8.26.0263', '0001425-02.2007.8.26.0266', '0005026-68.2011.8.26.0268', '0008068-48.1999.8.26.0268', '0008527-16.2000.8.26.0268', '2000013-41.1994.8.26.0271', '2000014-50.1999.8.26.0271', '2000022-37.1993.8.26.0271', '2000024-07.1993.8.26.0271', '2000037-64.1997.8.26.0271', '0001515-91.1995.8.26.0278']</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -6185,23 +7341,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
         <is>
           <t>0002232-35.1997.8.26.0278</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6269,13 +7439,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K61" t="n">
+      <c r="Q61" t="n">
         <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>['0002232-35.1997.8.26.0278', '0001409-42.1994.8.26.0286', '0002526-86.1999.8.26.0288', '0000559-94.1999.8.26.0291', '0004549-15.2007.8.26.0291', '0002479-13.1993.8.26.0292', '0015855-80.2004.8.26.0292', '0016691-72.2012.8.26.0292']</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -6289,23 +7464,37 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
         <is>
           <t>0503561-02.2005.8.26.0292</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6373,13 +7562,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K62" t="n">
+      <c r="Q62" t="n">
         <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>['0503561-02.2005.8.26.0292', '0509311-09.2010.8.26.0292', '0509318-98.2010.8.26.0292', '0005608-58.2009.8.26.0294', '0000180-95.2000.8.26.0299', '0000271-06.2005.8.26.0302', '0003174-97.1994.8.26.0302']</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -6393,23 +7587,37 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
         <is>
           <t>0008652-18.1996.8.26.0302</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6477,13 +7685,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K63" t="n">
+      <c r="Q63" t="n">
         <v>0</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>['0008652-18.1996.8.26.0302', '0010363-48.2002.8.26.0302', '0016469-16.2008.8.26.0302', '0021457-75.2011.8.26.0302', '0500260-02.2014.8.26.0302', '1504358-32.2022.8.26.0302', '0004818-20.1995.8.26.0309', '0008698-20.1995.8.26.0309', '0010224-17.1998.8.26.0309', '0011231-15.1996.8.26.0309', '0020492-13.2010.8.26.0309', '0023396-21.2001.8.26.0309', '0003897-63.1997.8.26.0318', '0010505-96.2005.8.26.0318', '0007940-51.2008.8.26.0320', '0009869-71.1998.8.26.0320']</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -6497,23 +7710,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
         <is>
           <t>0000022-56.1986.8.26.0323</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6581,13 +7808,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K64" t="n">
+      <c r="Q64" t="n">
         <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>['0000022-56.1986.8.26.0323', '0000035-50.1989.8.26.0323', '0000490-96.2000.8.26.0333']</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -6601,23 +7833,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
         <is>
           <t>1510279-29.2020.8.26.0338</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6685,13 +7931,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K65" t="n">
+      <c r="Q65" t="n">
         <v>0</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>['0008284-14.1995.8.26.0344', '0027308-13.2004.8.26.0344', '0000001-97.1989.8.26.0348', '0002450-18.1995.8.26.0348', '0012639-64.2009.8.26.0348', '0022526-38.2010.8.26.0348', '2000368-92.1986.8.26.0348', '0006931-02.2006.8.26.0360', '0000018-27.1971.8.26.0361']</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -6705,23 +7956,37 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
         <is>
           <t>0000183-83.1985.8.26.0361</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6790,13 +8055,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K66" t="n">
+      <c r="Q66" t="n">
         <v>0</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>['0000183-83.1985.8.26.0361', '0000568-65.1984.8.26.0361', '0000905-83.1986.8.26.0361', '0000961-48.1988.8.26.0361', '0002380-88.1997.8.26.0361', '0003270-71.1990.8.26.0361', '0003271-56.1990.8.26.0361', '0004165-46.2001.8.26.0361', '0005916-10.1997.8.26.0361', '0006194-88.2009.8.26.0361', '0000105-42.1992.8.26.0362', '0006436-64.1997.8.26.0362', '0007331-88.1998.8.26.0362', '0011433-70.2009.8.26.0362', '0001327-95.1999.8.26.0363']</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -6810,23 +8080,37 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
         <is>
           <t>0001327-95.1999.8.26.0363</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6894,13 +8178,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K67" t="n">
+      <c r="Q67" t="n">
         <v>0</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>['0002310-16.2007.8.26.0363', '0002438-70.2006.8.26.0363', '0003537-75.2006.8.26.0363', '0000031-97.1997.8.26.0366', '0001860-45.1999.8.26.0366', '0002439-51.2003.8.26.0366', '0003142-74.2006.8.26.0366', '0005433-81.2005.8.26.0366', '0006594-47.2010.8.26.0368', '0001107-45.2001.8.26.0390', '0001363-51.2002.8.26.0390', '0003392-74.2002.8.26.0390', '0003552-65.2003.8.26.0390']</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -6914,23 +8203,37 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
         <is>
           <t>0002033-43.2003.8.26.0394</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -6999,13 +8302,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K68" t="n">
+      <c r="Q68" t="n">
         <v>0</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>['0002033-43.2003.8.26.0394', '0000125-57.1999.8.26.0404', '0000387-02.2002.8.26.0404', '0000413-39.1998.8.26.0404', '0000414-24.1998.8.26.0404', '0000664-42.2007.8.26.0404', '0002123-89.2001.8.26.0404', '0004350-37.2010.8.26.0404', '0004492-90.2000.8.26.0404', '0004520-38.2012.8.26.0404', '0004520-38.2012.8.26.0404', '0004547-21.2012.8.26.0404', '0008272-11.1995.8.26.0405', '0009731-14.1996.8.26.0405', '0027161-71.1999.8.26.0405']</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -7019,23 +8327,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
         <is>
           <t>1020061-13.2020.8.26.0405</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -7102,13 +8424,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K69" t="n">
+      <c r="Q69" t="n">
         <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>['1020061-13.2020.8.26.0405', '0000090-15.2004.8.26.0407', '0007948-87.2010.8.26.0407', '1000588-40.2017.8.26.0407', '1500971-82.2022.8.26.0407', '0004150-82.2005.8.26.0411', '1002038-06.2017.8.26.0411', '0000613-02.2001.8.26.0417', '0001058-39.2005.8.26.0430']</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -7122,23 +8449,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
         <is>
           <t>0006467-32.2001.8.26.0431</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -7203,13 +8544,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K70" t="n">
+      <c r="Q70" t="n">
         <v>0</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>['0006467-32.2001.8.26.0431', '0007064-98.2001.8.26.0431', '0000645-19.2002.8.26.0434', '1003361-77.2022.8.26.0441', '3001971-53.2013.8.26.0441', '0001107-06.2003.8.26.0445', '0003633-87.1996.8.26.0445', '0011814-57.2008.8.26.0445', '0000310-20.2000.8.26.0450', '0008755-63.1996.8.26.0451']</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -7223,23 +8569,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
         <is>
           <t>0038244-72.2001.8.26.0451</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -7306,13 +8666,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K71" t="n">
+      <c r="Q71" t="n">
         <v>0</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>['0000114-15.1998.8.26.0452', '1002843-59.2019.8.26.0452', '0001851-80.2008.8.26.0459', '0007154-22.2001.8.26.0459', '0001021-06.2002.8.26.0466', '0002320-42.2007.8.26.0466', '0003335-02.2014.8.26.0466', '0000557-32.2000.8.26.0472']</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -7326,23 +8691,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
         <is>
           <t>0000557-32.2000.8.26.0472</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -7409,13 +8788,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K72" t="n">
+      <c r="Q72" t="n">
         <v>0</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>['0001687-52.1994.8.26.0477', '0003703-76.1994.8.26.0477', '0012389-49.2011.8.26.0481', '1001388-06.2018.8.26.0481', '1503247-58.2022.8.26.0481', '0009797-25.1994.8.26.0482', '1003035-90.2019.8.26.0484', '0001493-29.2002.8.26.0491', '0002057-37.2004.8.26.0491', '0002528-24.2002.8.26.0491', '0005732-42.2003.8.26.0491']</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -7429,23 +8813,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
         <is>
           <t>0001027-67.2009.8.26.0498</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -7516,13 +8914,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K73" t="n">
+      <c r="Q73" t="n">
         <v>0</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>['0003986-34.2002.8.26.0505', '0005703-47.2003.8.26.0505', '0006108-10.2008.8.26.0505']</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -7536,23 +8939,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
         <is>
           <t>0005226-70.1993.8.26.0506</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -7622,13 +9039,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K74" t="n">
+      <c r="Q74" t="n">
         <v>0</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>['0005226-70.1993.8.26.0506', '0017061-21.1994.8.26.0506', '0021463-91.2007.8.26.0506', '0025082-87.2011.8.26.0506', '0026164-18.1995.8.26.0506', '1023823-35.2014.8.26.0506', '0003007-91.2001.8.26.0510', '0018025-89.2000.8.26.0510']</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -7642,23 +9064,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
         <is>
           <t>0501647-15.2011.8.26.0510</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -7723,13 +9159,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K75" t="n">
+      <c r="Q75" t="n">
         <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>['0005522-02.2007.8.26.0539', '0001728-74.2001.8.26.0541', '0000948-52.1997.8.26.0549', '0005087-37.1994.8.26.0554', '0005088-22.1994.8.26.0554', '0006730-64.1993.8.26.0554']</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -7743,27 +9184,41 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>civel_estadual</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ademilde de Jesus da Silva</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
+          <t>maximo</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ademilde De Jesus Da Silva</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
         <is>
           <t>0011006-36.1996.8.26.0554</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -7832,13 +9287,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K76" t="n">
+      <c r="Q76" t="n">
         <v>0</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>['0011006-36.1996.8.26.0554', '0024508-42.1996.8.26.0554', '0027060-19.1992.8.26.0554', '0030934-65.1999.8.26.0554', '0000657-23.1991.8.26.0562', '0029735-52.1997.8.26.0562', '1000360-33.1990.8.26.0562', '1007617-70.1994.8.26.0562', '1008036-90.1994.8.26.0562']</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -7852,27 +9312,41 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>civel_estadual</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Carlos Ramos da Silva</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
+          <t>maximo</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Carlos Ramos Da Silva</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
         <is>
           <t>0018026-14.1997.8.26.0564</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -7939,13 +9413,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K77" t="n">
+      <c r="Q77" t="n">
         <v>0</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>['0003091-09.2010.8.26.0565', '0005670-76.2000.8.26.0565', '0007247-55.2001.8.26.0565', '2001606-24.1979.8.26.0565', '0000509-19.1999.8.26.0566', '0012353-43.2011.8.26.0566', '0007015-71.2005.8.26.0575']</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -7959,23 +9438,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
         <is>
           <t>0000523-77.1993.8.26.0577</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -8044,13 +9537,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K78" t="n">
+      <c r="Q78" t="n">
         <v>0</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>['0000523-77.1993.8.26.0577', '1028097-81.2018.8.26.0577', '0000018-72.2001.8.26.0588', '0000755-75.2001.8.26.0588', '2050008-37.1997.8.26.0588']</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -8064,23 +9562,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
         <is>
           <t>0530016-12.2007.8.26.0590</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -8149,13 +9661,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K79" t="n">
+      <c r="Q79" t="n">
         <v>0</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>['0003732-43.2006.8.26.0595', '0003301-52.1996.8.26.0597']</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -8169,23 +9686,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
         <is>
           <t>1507081-75.2023.8.26.0597</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -8252,13 +9783,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K80" t="n">
+      <c r="Q80" t="n">
         <v>0</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>['0003321-80.2000.8.26.0604', '0003598-38.1996.8.26.0604', '0012754-88.2012.8.26.0604', '0013006-62.2010.8.26.0604', '0000285-74.2007.8.26.0607', '0000621-29.1994.8.26.0609', '0003593-98.1996.8.26.0609', '0002353-63.2004.8.26.0619', '0004669-78.2006.8.26.0619']</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -8272,23 +9808,37 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
         <is>
           <t>1002357-48.2025.8.26.0619</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -8355,13 +9905,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K81" t="n">
+      <c r="Q81" t="n">
         <v>0</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>['1002357-48.2025.8.26.0619', '0000476-17.1997.8.26.0625', '0001543-07.2003.8.26.0625', '0003114-52.1999.8.26.0625', '0004004-30.1995.8.26.0625', '0008591-90.1998.8.26.0625', '0009197-84.1999.8.26.0625', '0021560-30.2004.8.26.0625', '0507340-91.2009.8.26.0625', '1500716-28.2017.8.26.0625', '1502311-28.2018.8.26.0625', '1505526-80.2016.8.26.0625', '1518980-59.2018.8.26.0625', '0000218-09.1999.8.26.0634', '1001960-41.2025.8.26.0634', '0003096-87.2002.8.26.0637']</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -8375,23 +9930,37 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>civel_estadual</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>maximo</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
         <is>
           <t>0517009-25.2006.8.26.0642</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr">
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -8445,13 +10014,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K82" t="n">
+      <c r="Q82" t="n">
         <v>0</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>['0517009-25.2006.8.26.0642', '0000004-67.1999.8.26.0650', '0000616-10.1996.8.26.0650', '0001428-52.1996.8.26.0650', '0000469-15.2009.8.26.0654', '0000127-26.1994.8.26.0655', '0000296-76.1995.8.26.0655', '0000614-64.1992.8.26.0655', '1000078-26.1998.8.26.0655']</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -8465,27 +10039,41 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>civel_estadual</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>pesquisado figura como autor</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
+          <t>maximo</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Pesquisado Figura Como Autor</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
         <is>
           <t>1000517-55.2018.8.26.0681</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
         <is>
           <t>0094491019
 02/03/2026
@@ -8522,13 +10110,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K83" t="n">
+      <c r="Q83" t="n">
         <v>0</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>['1000517-55.2018.8.26.0681']</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -8542,23 +10135,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
+          <t>criminal_estadual</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
         <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
         <is>
           <t>0095363181
 31/03/2026
@@ -8584,13 +10191,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K84" t="n">
+      <c r="Q84" t="n">
         <v>0</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -8604,31 +10216,45 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>civel_estadual</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>em nome de</t>
+          <t>maximo</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>Em Nome De</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>300.892.878-19</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>0034647-39.1968.8.26.0100</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr">
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
         <is>
           <t>0094490973
 02/03/2026
@@ -8677,13 +10303,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K85" t="n">
+      <c r="Q85" t="n">
         <v>0</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>['0034647-39.1968.8.26.0100', '0034652-61.1968.8.26.0100', '0034711-73.1973.8.26.0100']</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -8697,23 +10328,37 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>civel_estadual</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>de pessoa jurídica considera os processos referentes à matriz e às filiais e poderá apontar feitos de homônimos não qualificados com tipos empresariais diferentes do nome indicado na certidão</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>maximo</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>De Pessoa Jurídica Considera Os Processos Referentes À Matriz E Às Filiais E Poderá Apontar Feitos De Homônimos Não Qualificados Com Tipos Empresariais Diferentes Do Nome Indicado Na Certidão</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr">
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
         <is>
           <t>0094490973
 02/03/2026
@@ -8734,13 +10379,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K86" t="n">
+      <c r="Q86" t="n">
         <v>0</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -8754,27 +10404,41 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>civel_estadual</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>em nome de</t>
+          <t>maximo</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>Em Nome De</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
         <is>
           <t>0095363148
 31/03/2026
@@ -8814,13 +10478,18 @@
 PEDIDO N°:</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K87" t="n">
+      <c r="Q87" t="n">
         <v>0</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -8834,27 +10503,41 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -8890,13 +10573,18 @@
 - Sistema Eletrônico de Execução Unificado até 31/03/2026 , às 06:57:12.</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K88" t="n">
+      <c r="Q88" t="n">
         <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -8910,28 +10598,47 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>desconhecido</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr">
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
         <is>
           <t>Código de validação: 5GPS.V7SA.L8QC.0OQB.43VW
 Para conferir a autenticidade desta certidão, capture o QR Code ou acesse o site
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/5GPS.V7SA.L8QC.0OQB.43VW</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K89" t="n">
+      <c r="Q89" t="n">
         <v>0</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -8945,27 +10652,41 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr">
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -9001,13 +10722,18 @@
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/5GPS.V7SA.L8QC.0OQB.43VW</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K90" t="n">
+      <c r="Q90" t="n">
         <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -9021,27 +10747,41 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -9080,13 +10820,18 @@
 - TEBAS até 03/02/2026 , às 10:31:27.</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K91" t="n">
+      <c r="Q91" t="n">
         <v>0</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -9100,28 +10845,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>desconhecido</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
         <is>
           <t>Código de validação: 5GPS.V7SA.L8QC.0OQB.43VW
 Para conferir a autenticidade desta certidão, capture o QR Code ou acesse o site
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/5GPS.V7SA.L8QC.0OQB.43VW</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K92" t="n">
+      <c r="Q92" t="n">
         <v>0</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -9135,27 +10899,41 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr">
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -9192,13 +10970,18 @@
 - Sistema Eletrônico de Execução Unificado até 31/03/2026 , às 06:57:12.</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K93" t="n">
+      <c r="Q93" t="n">
         <v>0</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -9212,28 +10995,47 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>desconhecido</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr">
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
         <is>
           <t>Código de validação: LEET.XH7P.QNN9.O69H.I6EU
 Para conferir a autenticidade desta certidão, capture o QR Code ou acesse o site
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/LEET.XH7P.QNN9.O69H.I6EU</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K94" t="n">
+      <c r="Q94" t="n">
         <v>0</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -9247,27 +11049,41 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr">
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -9304,13 +11120,18 @@
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/LEET.XH7P.QNN9.O69H.I6EU</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K95" t="n">
+      <c r="Q95" t="n">
         <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -9324,27 +11145,41 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -9381,13 +11216,18 @@
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/LEET.XH7P.QNN9.O69H.I6EU</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K96" t="n">
+      <c r="Q96" t="n">
         <v>0</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -9401,27 +11241,41 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr">
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -9461,13 +11315,18 @@
 - TEBAS até 03/02/2026 , às 10:31:27.</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K97" t="n">
+      <c r="Q97" t="n">
         <v>0</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -9481,28 +11340,47 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>desconhecido</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr">
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
         <is>
           <t>Código de validação: LEET.XH7P.QNN9.O69H.I6EU
 Para conferir a autenticidade desta certidão, capture o QR Code ou acesse o site
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/LEET.XH7P.QNN9.O69H.I6EU</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="P98" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K98" t="n">
+      <c r="Q98" t="n">
         <v>0</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -9516,27 +11394,41 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr">
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -9573,13 +11465,18 @@
 - Sistema Eletrônico de Execução Unificado até 31/03/2026 , às 06:57:12.</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K99" t="n">
+      <c r="Q99" t="n">
         <v>0</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -9593,28 +11490,47 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>desconhecido</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr">
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
         <is>
           <t>Código de validação: DBXK.SGAC.31EY.OE3E.BTS7
 Para conferir a autenticidade desta certidão, capture o QR Code ou acesse o site
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/DBXK.SGAC.31EY.OE3E.BTS7</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K100" t="n">
+      <c r="Q100" t="n">
         <v>0</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -9628,27 +11544,41 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -9685,13 +11615,18 @@
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/DBXK.SGAC.31EY.OE3E.BTS7</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K101" t="n">
+      <c r="Q101" t="n">
         <v>0</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -9705,27 +11640,41 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
+          <t>trf3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>informativo</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>977.326.998-15</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr">
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
         <is>
           <t>PODER JUDICIÁRIO
 JUSTIÇA FEDERAL
@@ -9765,13 +11714,18 @@
 - TEBAS até 03/02/2026 , às 10:31:27.</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K102" t="n">
+      <c r="Q102" t="n">
         <v>0</v>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -9785,28 +11739,47 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>certidao_tj</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>desconhecido</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>informativo</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr">
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>POSITIVA</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
         <is>
           <t>Código de validação: DBXK.SGAC.31EY.OE3E.BTS7
 Para conferir a autenticidade desta certidão, capture o QR Code ou acesse o site
 https://certidao-unificada.cjf.jus.br/#/validacao-certidao/DBXK.SGAC.31EY.OE3E.BTS7</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>plumber</t>
         </is>
       </c>
-      <c r="K103" t="n">
+      <c r="Q103" t="n">
         <v>0</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
   </sheetData>
